--- a/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/data/D4_mapping_params.xlsx
+++ b/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/data/D4_mapping_params.xlsx
@@ -19,7 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -58,11 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,1961 +432,5163 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:Y51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>regime_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>subscore</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>risk_metric</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>q50</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>q75</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>q90</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>q97_5</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>sample_size</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>exact_stratum_size</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>independent_blocks</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>exact_independent_blocks</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>mapping_scope</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>calibration_quality</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mapping_role</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>fit_phase</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>fit_start</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>fit_end</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>configured_fit_start</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>configured_fit_end</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>common_support_policy</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>distribution_component_version</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>benchmark_source</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mapping_type</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>mapping_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>variable</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>regime_id</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>subscore</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>risk_metric</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>q50</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>q75</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>q90</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>q97_5</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>sample_size</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>exact_stratum_size</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mapping_scope</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>calibration_quality</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>benchmark_source</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>mapping_type</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DO-R2.0-Q_dist</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="B2" t="n">
         <v>2</v>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Q_dist</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Q_dist</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
           <t>risk_dist</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>0.2242068456339798</v>
+      </c>
       <c r="F2" t="n">
-        <v>0.2181624540335634</v>
+        <v>0.3215925734470796</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3133887134903199</v>
+        <v>0.4422025352366835</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4291660232066167</v>
+        <v>0.701367504591667</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7052089229378596</v>
+        <v>1106</v>
       </c>
       <c r="J2" t="n">
-        <v>1060</v>
+        <v>1106</v>
       </c>
       <c r="K2" t="n">
-        <v>1060</v>
-      </c>
-      <c r="L2" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
-        </is>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>45871.91666666666</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>45912.08333333334</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>DO-R2.0-Q_dist-420c6950886d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DO-R2.0-Q_trend</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="B3" t="n">
         <v>2</v>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Q_dist_w1_candidate</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Q_trend</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>risk_trend</t>
-        </is>
+          <t>risk_dist_w1</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.2581658218107801</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6089235361301848</v>
+        <v>0.381709154821665</v>
       </c>
       <c r="G3" t="n">
-        <v>1.033520067229793</v>
+        <v>0.5257618258433355</v>
       </c>
       <c r="H3" t="n">
-        <v>1.444743793346957</v>
+        <v>0.854549779925993</v>
       </c>
       <c r="I3" t="n">
-        <v>1.920689454334735</v>
+        <v>1106</v>
       </c>
       <c r="J3" t="n">
-        <v>1060</v>
+        <v>1106</v>
       </c>
       <c r="K3" t="n">
-        <v>1060</v>
-      </c>
-      <c r="L3" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
-        </is>
-      </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>construct_ablation_only</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>45871.91666666666</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>45912.08333333334</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>DO-R2.0-Q_dist_w1_candidate-5d2974501d82</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DO-R2.0-Q_var</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="B4" t="n">
         <v>2</v>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Q_dist_ks_candidate</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Q_var</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>risk_var</t>
-        </is>
+          <t>risk_dist_ks</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1597222222222223</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1181693395333395</v>
+        <v>0.2361111111111112</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2044106032792038</v>
+        <v>0.3194444444444444</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3596491722370428</v>
+        <v>0.5512152777777778</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7546981250170745</v>
+        <v>1106</v>
       </c>
       <c r="J4" t="n">
-        <v>1060</v>
+        <v>1106</v>
       </c>
       <c r="K4" t="n">
-        <v>1060</v>
-      </c>
-      <c r="L4" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
-        </is>
-      </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>construct_ablation_only</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>45871.91666666666</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>45912.08333333334</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>DO-R2.0-Q_dist_ks_candidate-2edb3e90b80b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DO-R3.0-Q_dist</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>3</v>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Q_trend</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Q_dist</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>risk_dist</t>
-        </is>
+          <t>risk_trend</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.5915952324260325</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4755043423023069</v>
+        <v>1.016905183633807</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6924955311560432</v>
+        <v>1.435823379197355</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8885957586485553</v>
+        <v>1.902622674488252</v>
       </c>
       <c r="I5" t="n">
-        <v>1.122775053764726</v>
+        <v>1106</v>
       </c>
       <c r="J5" t="n">
-        <v>524</v>
+        <v>1106</v>
       </c>
       <c r="K5" t="n">
-        <v>524</v>
-      </c>
-      <c r="L5" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
-        </is>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>45871.91666666666</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>45912.08333333334</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>DO-R2.0-Q_trend-b84f1267d372</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DO-R3.0-Q_trend</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>3</v>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Q_var</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Q_trend</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>risk_trend</t>
-        </is>
+          <t>risk_var</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1162559437308746</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9483776611868711</v>
+        <v>0.204251320631778</v>
       </c>
       <c r="G6" t="n">
-        <v>1.575393096538618</v>
+        <v>0.3564043461481126</v>
       </c>
       <c r="H6" t="n">
-        <v>2.281514551029057</v>
+        <v>0.7532075929631925</v>
       </c>
       <c r="I6" t="n">
-        <v>3.295138565271943</v>
+        <v>1106</v>
       </c>
       <c r="J6" t="n">
-        <v>524</v>
+        <v>1106</v>
       </c>
       <c r="K6" t="n">
-        <v>524</v>
-      </c>
-      <c r="L6" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
-        </is>
-      </c>
       <c r="O6" t="inlineStr">
         <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>45871.91666666666</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>45912.08333333334</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>DO-R2.0-Q_var-c3b49167d4c9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DO-R3.0-Q_var</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="B7" t="n">
         <v>3</v>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Q_dist</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Q_var</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>risk_var</t>
-        </is>
+          <t>risk_dist</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.4755043423023069</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4236001924571131</v>
+        <v>0.6924955311560432</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7655761868625628</v>
+        <v>0.8885957586485553</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9589430132834768</v>
+        <v>1.122775053764726</v>
       </c>
       <c r="I7" t="n">
-        <v>1.191281151644254</v>
+        <v>524</v>
       </c>
       <c r="J7" t="n">
         <v>524</v>
       </c>
       <c r="K7" t="n">
-        <v>524</v>
-      </c>
-      <c r="L7" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
-        </is>
-      </c>
       <c r="O7" t="inlineStr">
         <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>45914.125</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>45955.70833333334</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>DO-R3.0-Q_dist-80297c6b6abe</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DO-R1.0-Q_dist</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>1</v>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Q_dist_w1_candidate</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Q_dist</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>risk_dist</t>
-        </is>
+          <t>risk_dist_w1</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5594012354425311</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2525203916251205</v>
+        <v>0.7912258537402233</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3366883036277407</v>
+        <v>1.103251989120996</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4478292672257014</v>
+        <v>1.42792365047316</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6098356108735087</v>
+        <v>524</v>
       </c>
       <c r="J8" t="n">
-        <v>746</v>
+        <v>524</v>
       </c>
       <c r="K8" t="n">
-        <v>746</v>
-      </c>
-      <c r="L8" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
-        </is>
-      </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>construct_ablation_only</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>45914.125</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>45955.70833333334</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>DO-R3.0-Q_dist_w1_candidate-447872a6342c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DO-R1.0-Q_trend</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>1</v>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Q_dist_ks_candidate</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Q_trend</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>risk_trend</t>
-        </is>
+          <t>risk_dist_ks</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.3333333333333333</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7007107543841994</v>
+        <v>0.4930555555555556</v>
       </c>
       <c r="G9" t="n">
-        <v>1.206309098179878</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="H9" t="n">
-        <v>1.621040132442261</v>
+        <v>0.7361111111111112</v>
       </c>
       <c r="I9" t="n">
-        <v>2.283836091422137</v>
+        <v>524</v>
       </c>
       <c r="J9" t="n">
-        <v>746</v>
+        <v>524</v>
       </c>
       <c r="K9" t="n">
-        <v>746</v>
-      </c>
-      <c r="L9" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
-        </is>
-      </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>construct_ablation_only</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>45914.125</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>45955.70833333334</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>DO-R3.0-Q_dist_ks_candidate-07a99340fe92</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DO-R1.0-Q_var</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>1</v>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Q_trend</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Q_var</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>risk_var</t>
-        </is>
+          <t>risk_trend</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9483776611868711</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1247248170852662</v>
+        <v>1.575393096538618</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2581888438171047</v>
+        <v>2.281514551029057</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3843851985421037</v>
+        <v>3.295138565271943</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5726308411157923</v>
+        <v>524</v>
       </c>
       <c r="J10" t="n">
-        <v>746</v>
+        <v>524</v>
       </c>
       <c r="K10" t="n">
-        <v>746</v>
-      </c>
-      <c r="L10" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
-        </is>
-      </c>
       <c r="O10" t="inlineStr">
         <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>45914.125</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>45955.70833333334</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>DO-R3.0-Q_trend-27029d7092e4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DO-R0.0-Q_dist</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>0</v>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Q_var</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Q_dist</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>risk_dist</t>
-        </is>
+          <t>risk_var</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.4236001924571131</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2167665307866929</v>
+        <v>0.7655761868625628</v>
       </c>
       <c r="G11" t="n">
-        <v>0.300769119446163</v>
+        <v>0.9589430132834768</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3932498291761582</v>
+        <v>1.191281151644254</v>
       </c>
       <c r="I11" t="n">
-        <v>0.561422390573258</v>
+        <v>524</v>
       </c>
       <c r="J11" t="n">
-        <v>2316</v>
+        <v>524</v>
       </c>
       <c r="K11" t="n">
-        <v>2316</v>
-      </c>
-      <c r="L11" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
-        </is>
-      </c>
       <c r="O11" t="inlineStr">
         <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>45914.125</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>45955.70833333334</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>DO-R3.0-Q_var-1708a867e09c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DO-R0.0-Q_trend</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>0</v>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Q_dist</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Q_trend</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>risk_trend</t>
-        </is>
+          <t>risk_dist</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.2499879171730521</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6816065607760247</v>
+        <v>0.3336336992342119</v>
       </c>
       <c r="G12" t="n">
-        <v>1.118979995521794</v>
+        <v>0.4478657099260334</v>
       </c>
       <c r="H12" t="n">
-        <v>1.583698469451417</v>
+        <v>0.6106940394547403</v>
       </c>
       <c r="I12" t="n">
-        <v>2.130126683566745</v>
+        <v>732</v>
       </c>
       <c r="J12" t="n">
-        <v>2316</v>
+        <v>732</v>
       </c>
       <c r="K12" t="n">
-        <v>2316</v>
-      </c>
-      <c r="L12" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
-        </is>
-      </c>
       <c r="O12" t="inlineStr">
         <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>45946.91666666666</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>46023.91666666666</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>DO-R1.0-Q_dist-07fec55c78e8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DO-R0.0-Q_var</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>0</v>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Q_dist_w1_candidate</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Q_var</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>risk_var</t>
-        </is>
+          <t>risk_dist_w1</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.276793366771523</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1408893020387061</v>
+        <v>0.3919622533530995</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2523063720237416</v>
+        <v>0.5333821514560001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.403795376447266</v>
+        <v>0.6846838779050404</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5502059101881052</v>
+        <v>732</v>
       </c>
       <c r="J13" t="n">
-        <v>2316</v>
+        <v>732</v>
       </c>
       <c r="K13" t="n">
-        <v>2316</v>
-      </c>
-      <c r="L13" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="L13" t="n">
+        <v>11</v>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
-        </is>
-      </c>
       <c r="O13" t="inlineStr">
         <is>
+          <t>construct_ablation_only</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>45946.91666666666</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>46023.91666666666</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>DO-R1.0-Q_dist_w1_candidate-4d9a797bee8f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DO-Rnan-Q_dist</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Q_dist_ks_candidate</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Q_dist</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>risk_dist</t>
-        </is>
+          <t>risk_dist_ks</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.2013888888888889</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2379118056706658</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3413532390203972</v>
+        <v>0.3402777777777778</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4974344750457913</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="I14" t="n">
-        <v>0.778035562034328</v>
+        <v>732</v>
       </c>
       <c r="J14" t="n">
-        <v>4646</v>
+        <v>732</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>variable_public_fallback</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="L14" t="n">
+        <v>11</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>limited_regime_support</t>
+          <t>variable_regime_public</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
+          <t>adequate</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
+          <t>construct_ablation_only</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>45946.91666666666</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>46023.91666666666</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>DO-R1.0-Q_dist_ks_candidate-09bf2c99beb2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DO-Rnan-Q_trend</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Q_trend</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Q_trend</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
           <t>risk_trend</t>
         </is>
       </c>
+      <c r="E15" t="n">
+        <v>0.7007107543841994</v>
+      </c>
       <c r="F15" t="n">
-        <v>0.6881375672118664</v>
+        <v>1.209598441824764</v>
       </c>
       <c r="G15" t="n">
-        <v>1.15244555063635</v>
+        <v>1.629994569936485</v>
       </c>
       <c r="H15" t="n">
-        <v>1.617401398170177</v>
+        <v>2.287400709034298</v>
       </c>
       <c r="I15" t="n">
-        <v>2.315373671580646</v>
+        <v>732</v>
       </c>
       <c r="J15" t="n">
-        <v>4646</v>
+        <v>732</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>variable_public_fallback</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="L15" t="n">
+        <v>11</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>limited_regime_support</t>
+          <t>variable_regime_public</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
+          <t>adequate</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>45946.91666666666</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>46023.91666666666</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>DO-R1.0-Q_trend-dcdbf54f940a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DO-Rnan-Q_var</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Q_var</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Q_var</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
           <t>risk_var</t>
         </is>
       </c>
+      <c r="E16" t="n">
+        <v>0.1211935786645841</v>
+      </c>
       <c r="F16" t="n">
-        <v>0.1440469446085341</v>
+        <v>0.2486594477418825</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2784318203557657</v>
+        <v>0.3846866939720698</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4750291623422657</v>
+        <v>0.5750717998821897</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8501314147501072</v>
+        <v>732</v>
       </c>
       <c r="J16" t="n">
-        <v>4646</v>
+        <v>732</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>variable_public_fallback</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="L16" t="n">
+        <v>11</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>limited_regime_support</t>
+          <t>variable_regime_public</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
+          <t>adequate</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>45946.91666666666</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>46023.91666666666</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>DO-R1.0-Q_var-7f5460ae7a39</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORP-R2.0-Q_dist</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ORP</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Q_dist</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Q_dist</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
           <t>risk_dist</t>
         </is>
       </c>
+      <c r="E17" t="n">
+        <v>0.2415382575363332</v>
+      </c>
       <c r="F17" t="n">
-        <v>0.2759997578094889</v>
+        <v>0.3316552601602292</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4197024771651728</v>
+        <v>0.4263320303922709</v>
       </c>
       <c r="H17" t="n">
-        <v>0.479798045086721</v>
+        <v>0.7956133799211891</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5939238998259706</v>
+        <v>569</v>
       </c>
       <c r="J17" t="n">
-        <v>145</v>
+        <v>569</v>
       </c>
       <c r="K17" t="n">
-        <v>145</v>
-      </c>
-      <c r="L17" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5</v>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
-        </is>
-      </c>
       <c r="O17" t="inlineStr">
         <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>46046.95833333334</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T17" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>DO-R0.0-Q_dist-ca8755d8a837</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORP-R2.0-Q_trend</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ORP</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>2</v>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Q_dist_w1_candidate</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Q_trend</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>risk_trend</t>
-        </is>
+          <t>risk_dist_w1</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.2729341329309258</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6217121253038793</v>
+        <v>0.3682957277430781</v>
       </c>
       <c r="G18" t="n">
-        <v>1.142374564881111</v>
+        <v>0.5043476698092657</v>
       </c>
       <c r="H18" t="n">
-        <v>1.728859220681275</v>
+        <v>1.000731211715054</v>
       </c>
       <c r="I18" t="n">
-        <v>2.256419477775076</v>
+        <v>569</v>
       </c>
       <c r="J18" t="n">
-        <v>145</v>
+        <v>569</v>
       </c>
       <c r="K18" t="n">
-        <v>145</v>
-      </c>
-      <c r="L18" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5</v>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
-        </is>
-      </c>
       <c r="O18" t="inlineStr">
         <is>
+          <t>construct_ablation_only</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>46046.95833333334</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>DO-R0.0-Q_dist_w1_candidate-b772003c9988</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORP-R2.0-Q_var</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ORP</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2</v>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Q_dist_ks_candidate</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Q_var</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>risk_var</t>
-        </is>
+          <t>risk_dist_ks</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.1805555555555556</v>
       </c>
       <c r="F19" t="n">
-        <v>0.04577498858176644</v>
+        <v>0.263888888888889</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3851290392046844</v>
+        <v>0.3472222222222222</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5449238159171348</v>
+        <v>0.5541666666666664</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7199690094883338</v>
+        <v>569</v>
       </c>
       <c r="J19" t="n">
-        <v>145</v>
+        <v>569</v>
       </c>
       <c r="K19" t="n">
-        <v>145</v>
-      </c>
-      <c r="L19" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5</v>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
-        </is>
-      </c>
       <c r="O19" t="inlineStr">
         <is>
+          <t>construct_ablation_only</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>46046.95833333334</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T19" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>DO-R0.0-Q_dist_ks_candidate-10ca77d0be6d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORP-R3.0-Q_dist</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ORP</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>3</v>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Q_trend</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Q_dist</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>risk_dist</t>
-        </is>
+          <t>risk_trend</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.6685884377276536</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3108362828864705</v>
+        <v>1.194327649593823</v>
       </c>
       <c r="G20" t="n">
-        <v>0.414384657314653</v>
+        <v>1.624472948677355</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5185623668249223</v>
+        <v>2.48238276335073</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7177497060330877</v>
+        <v>569</v>
       </c>
       <c r="J20" t="n">
-        <v>312</v>
+        <v>569</v>
       </c>
       <c r="K20" t="n">
-        <v>73</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>variable_public_fallback</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>limited_regime_support</t>
+          <t>variable_regime_public</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
+          <t>adequate</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>46046.95833333334</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T20" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>DO-R0.0-Q_trend-ae24d055f465</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORP-R3.0-Q_trend</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ORP</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>3</v>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Q_var</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Q_trend</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>risk_trend</t>
-        </is>
+          <t>risk_var</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.1088404493730298</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7177958739646288</v>
+        <v>0.2453041846419914</v>
       </c>
       <c r="G21" t="n">
-        <v>1.365266655703362</v>
+        <v>0.4390440437577821</v>
       </c>
       <c r="H21" t="n">
-        <v>1.883917248843737</v>
+        <v>0.6464672380740619</v>
       </c>
       <c r="I21" t="n">
-        <v>2.658382603775709</v>
+        <v>569</v>
       </c>
       <c r="J21" t="n">
-        <v>312</v>
+        <v>569</v>
       </c>
       <c r="K21" t="n">
-        <v>73</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>variable_public_fallback</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>limited_regime_support</t>
+          <t>variable_regime_public</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
+          <t>adequate</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>46046.95833333334</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T21" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>DO-R0.0-Q_var-c56483782a79</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORP-R3.0-Q_var</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ORP</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>3</v>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Q_dist</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Q_var</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>risk_var</t>
-        </is>
+          <t>risk_dist</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.2591372840258478</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2115030955240084</v>
+        <v>0.380449933519053</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3986814168111091</v>
+        <v>0.5762047423019866</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5466274877393715</v>
+        <v>0.8892579380559839</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7039127201392978</v>
+        <v>2931</v>
       </c>
       <c r="J22" t="n">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>73</v>
-      </c>
-      <c r="L22" t="inlineStr">
+        <v>26</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
-        </is>
-      </c>
       <c r="O22" t="inlineStr">
         <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>45871.91666666666</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>46046.95833333334</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>DO-Rnan-Q_dist-759f7f0cb608</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORP-R1.0-Q_dist</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ORP</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Q_dist_w1_candidate</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Q_dist</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>risk_dist</t>
-        </is>
+          <t>risk_dist_w1</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.2959161573281301</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3108362828864705</v>
+        <v>0.4427546011466684</v>
       </c>
       <c r="G23" t="n">
-        <v>0.414384657314653</v>
+        <v>0.6924811704768661</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5185623668249223</v>
+        <v>1.092517878419095</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7177497060330877</v>
+        <v>2931</v>
       </c>
       <c r="J23" t="n">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>32</v>
-      </c>
-      <c r="L23" t="inlineStr">
+        <v>26</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
-        </is>
-      </c>
       <c r="O23" t="inlineStr">
         <is>
+          <t>construct_ablation_only</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>45871.91666666666</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>46046.95833333334</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>DO-Rnan-Q_dist_w1_candidate-a59ac067fc51</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORP-R1.0-Q_trend</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ORP</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Q_dist_ks_candidate</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Q_trend</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>risk_trend</t>
-        </is>
+          <t>risk_dist_ks</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.1944444444444444</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7177958739646288</v>
+        <v>0.2916666666666666</v>
       </c>
       <c r="G24" t="n">
-        <v>1.365266655703362</v>
+        <v>0.4375</v>
       </c>
       <c r="H24" t="n">
-        <v>1.883917248843737</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="I24" t="n">
-        <v>2.658382603775709</v>
+        <v>2931</v>
       </c>
       <c r="J24" t="n">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>32</v>
-      </c>
-      <c r="L24" t="inlineStr">
+        <v>26</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
-        </is>
-      </c>
       <c r="O24" t="inlineStr">
         <is>
+          <t>construct_ablation_only</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>45871.91666666666</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>46046.95833333334</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>DO-Rnan-Q_dist_ks_candidate-477ff8d7f9ee</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORP-R1.0-Q_var</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ORP</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Q_trend</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Q_var</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>risk_var</t>
-        </is>
+          <t>risk_trend</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.6847658979444042</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2115030955240084</v>
+        <v>1.180487592297496</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3986814168111091</v>
+        <v>1.670805691840252</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5466274877393715</v>
+        <v>2.491753923646406</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7039127201392978</v>
+        <v>2931</v>
       </c>
       <c r="J25" t="n">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>32</v>
-      </c>
-      <c r="L25" t="inlineStr">
+        <v>26</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
-        </is>
-      </c>
       <c r="O25" t="inlineStr">
         <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>45871.91666666666</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>46046.95833333334</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T25" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>DO-Rnan-Q_trend-8290f3c9ad42</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORP-R0.0-Q_dist</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>ORP</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Q_var</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>risk_var</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.1396896366735182</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.3030325976890825</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.5503263956531718</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.9513555118284422</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2931</v>
+      </c>
+      <c r="J26" t="n">
         <v>0</v>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Q_dist</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>risk_dist</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>0.3108362828864705</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.414384657314653</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.5185623668249223</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.7177497060330877</v>
-      </c>
-      <c r="J26" t="n">
-        <v>312</v>
-      </c>
       <c r="K26" t="n">
-        <v>62</v>
-      </c>
-      <c r="L26" t="inlineStr">
+        <v>26</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
-        </is>
-      </c>
       <c r="O26" t="inlineStr">
         <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>45871.91666666666</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>46046.95833333334</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T26" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>DO-Rnan-Q_var-4c3b3f69641b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORP-R0.0-Q_trend</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
           <t>ORP</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>0</v>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Q_dist</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Q_trend</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>risk_trend</t>
-        </is>
+          <t>risk_dist</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.2691218105109053</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7177958739646288</v>
+        <v>0.4212200902414319</v>
       </c>
       <c r="G27" t="n">
-        <v>1.365266655703362</v>
+        <v>0.4861059399325525</v>
       </c>
       <c r="H27" t="n">
-        <v>1.883917248843737</v>
+        <v>0.8699482721940748</v>
       </c>
       <c r="I27" t="n">
-        <v>2.658382603775709</v>
+        <v>247</v>
       </c>
       <c r="J27" t="n">
-        <v>312</v>
+        <v>247</v>
       </c>
       <c r="K27" t="n">
-        <v>62</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>variable_public_fallback</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="L27" t="n">
+        <v>6</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>limited_regime_support</t>
+          <t>variable_regime_public</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
+          <t>adequate</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>45911.41666666666</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T27" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>ORP-R2.0-Q_dist-e53b83b86f17</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORP-R0.0-Q_var</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
           <t>ORP</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>0</v>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Q_dist_w1_candidate</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Q_var</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>risk_var</t>
-        </is>
+          <t>risk_dist_w1</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.3161372576288791</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2115030955240084</v>
+        <v>0.492752861668493</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3986814168111091</v>
+        <v>0.6108095985455346</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5466274877393715</v>
+        <v>1.030006379582717</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7039127201392978</v>
+        <v>247</v>
       </c>
       <c r="J28" t="n">
-        <v>312</v>
+        <v>247</v>
       </c>
       <c r="K28" t="n">
-        <v>62</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>variable_public_fallback</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>limited_regime_support</t>
+          <t>variable_regime_public</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
+          <t>adequate</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
+          <t>construct_ablation_only</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>45911.41666666666</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>ORP-R2.0-Q_dist_w1_candidate-822073356f41</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORP-Rnan-Q_dist</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
           <t>ORP</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Q_dist_ks_candidate</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Q_dist</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>risk_dist</t>
-        </is>
+          <t>risk_dist_ks</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.2222222222222222</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3108362828864705</v>
+        <v>0.2986111111111112</v>
       </c>
       <c r="G29" t="n">
-        <v>0.414384657314653</v>
+        <v>0.4263888888888889</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5185623668249223</v>
+        <v>0.629861111111111</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7177497060330877</v>
+        <v>247</v>
       </c>
       <c r="J29" t="n">
-        <v>312</v>
+        <v>247</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>variable_public_fallback</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>limited_regime_support</t>
+          <t>variable_regime_public</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
+          <t>adequate</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
+          <t>construct_ablation_only</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>45911.41666666666</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>ORP-R2.0-Q_dist_ks_candidate-ece56f157b83</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ORP-Rnan-Q_trend</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
           <t>ORP</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Q_trend</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Q_trend</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
           <t>risk_trend</t>
         </is>
       </c>
+      <c r="E30" t="n">
+        <v>0.6108778374157005</v>
+      </c>
       <c r="F30" t="n">
-        <v>0.7177958739646288</v>
+        <v>1.173005392961987</v>
       </c>
       <c r="G30" t="n">
-        <v>1.365266655703362</v>
+        <v>1.66780274413505</v>
       </c>
       <c r="H30" t="n">
-        <v>1.883917248843737</v>
+        <v>2.175890702142786</v>
       </c>
       <c r="I30" t="n">
-        <v>2.658382603775709</v>
+        <v>247</v>
       </c>
       <c r="J30" t="n">
-        <v>312</v>
+        <v>247</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>variable_public_fallback</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="L30" t="n">
+        <v>6</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>limited_regime_support</t>
+          <t>variable_regime_public</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
+          <t>adequate</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>45911.41666666666</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>ORP-R2.0-Q_trend-b5bbfa0475dd</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ORP-Rnan-Q_var</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
           <t>ORP</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Q_var</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>risk_var</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.03455685301696187</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.3312832879252339</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.5410230304796447</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.6985935489513286</v>
+      </c>
+      <c r="I31" t="n">
+        <v>247</v>
+      </c>
+      <c r="J31" t="n">
+        <v>247</v>
+      </c>
+      <c r="K31" t="n">
+        <v>6</v>
+      </c>
+      <c r="L31" t="n">
+        <v>6</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>variable_regime_public</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>adequate</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>45911.41666666666</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>ORP-R2.0-Q_var-9a9531abce4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Q_dist</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>risk_dist</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.31137029780911</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.4227377033176911</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.5618948284441422</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.8218040472452308</v>
+      </c>
+      <c r="I32" t="n">
+        <v>465</v>
+      </c>
+      <c r="J32" t="n">
+        <v>98</v>
+      </c>
+      <c r="K32" t="n">
+        <v>24</v>
+      </c>
+      <c r="L32" t="n">
+        <v>6</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>46046.5</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>ORP-R3.0-Q_dist-0811e8f4a3fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Q_dist_w1_candidate</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>risk_dist_w1</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.3426253184510224</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.4897517323509599</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.6599818427110471</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.9854141528161265</v>
+      </c>
+      <c r="I33" t="n">
+        <v>465</v>
+      </c>
+      <c r="J33" t="n">
+        <v>98</v>
+      </c>
+      <c r="K33" t="n">
+        <v>24</v>
+      </c>
+      <c r="L33" t="n">
+        <v>6</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>construct_ablation_only</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>46046.5</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T33" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>ORP-R3.0-Q_dist_w1_candidate-ee60a528da46</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Q_dist_ks_candidate</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>risk_dist_ks</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.3263888888888889</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.6138888888888888</v>
+      </c>
+      <c r="I34" t="n">
+        <v>465</v>
+      </c>
+      <c r="J34" t="n">
+        <v>98</v>
+      </c>
+      <c r="K34" t="n">
+        <v>24</v>
+      </c>
+      <c r="L34" t="n">
+        <v>6</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>construct_ablation_only</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>46046.5</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T34" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>ORP-R3.0-Q_dist_ks_candidate-9a3be7cda4d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Q_trend</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>risk_trend</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.759905590225795</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.336487910112083</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.08694363935768</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2.872750218451698</v>
+      </c>
+      <c r="I35" t="n">
+        <v>465</v>
+      </c>
+      <c r="J35" t="n">
+        <v>98</v>
+      </c>
+      <c r="K35" t="n">
+        <v>24</v>
+      </c>
+      <c r="L35" t="n">
+        <v>6</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>46046.5</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>ORP-R3.0-Q_trend-5ae5e101f465</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>Q_var</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>risk_var</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>0.2115030955240084</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.3986814168111091</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.5466274877393715</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.7039127201392978</v>
-      </c>
-      <c r="J31" t="n">
-        <v>312</v>
-      </c>
-      <c r="K31" t="n">
+      <c r="E36" t="n">
+        <v>0.2040077048153092</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.4024378858369875</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.5824132447081269</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.6934581704850538</v>
+      </c>
+      <c r="I36" t="n">
+        <v>465</v>
+      </c>
+      <c r="J36" t="n">
+        <v>98</v>
+      </c>
+      <c r="K36" t="n">
+        <v>24</v>
+      </c>
+      <c r="L36" t="n">
+        <v>6</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>46046.5</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T36" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>ORP-R3.0-Q_var-4603f19c2e35</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Q_dist</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>risk_dist</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.31137029780911</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.4227377033176911</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.5618948284441422</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.8218040472452308</v>
+      </c>
+      <c r="I37" t="n">
+        <v>465</v>
+      </c>
+      <c r="J37" t="n">
+        <v>97</v>
+      </c>
+      <c r="K37" t="n">
+        <v>24</v>
+      </c>
+      <c r="L37" t="n">
+        <v>10</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>46046.5</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>ORP-R1.0-Q_dist-f5a1c3e3fb3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Q_dist_w1_candidate</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>risk_dist_w1</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.3426253184510224</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.4897517323509599</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.6599818427110471</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.9854141528161265</v>
+      </c>
+      <c r="I38" t="n">
+        <v>465</v>
+      </c>
+      <c r="J38" t="n">
+        <v>97</v>
+      </c>
+      <c r="K38" t="n">
+        <v>24</v>
+      </c>
+      <c r="L38" t="n">
+        <v>10</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>construct_ablation_only</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>46046.5</v>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T38" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>ORP-R1.0-Q_dist_w1_candidate-b949fdc6dbb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Q_dist_ks_candidate</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>risk_dist_ks</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.3263888888888889</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.6138888888888888</v>
+      </c>
+      <c r="I39" t="n">
+        <v>465</v>
+      </c>
+      <c r="J39" t="n">
+        <v>97</v>
+      </c>
+      <c r="K39" t="n">
+        <v>24</v>
+      </c>
+      <c r="L39" t="n">
+        <v>10</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>construct_ablation_only</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>46046.5</v>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T39" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>ORP-R1.0-Q_dist_ks_candidate-b7073c096060</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Q_trend</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>risk_trend</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.759905590225795</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.336487910112083</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.08694363935768</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.872750218451698</v>
+      </c>
+      <c r="I40" t="n">
+        <v>465</v>
+      </c>
+      <c r="J40" t="n">
+        <v>97</v>
+      </c>
+      <c r="K40" t="n">
+        <v>24</v>
+      </c>
+      <c r="L40" t="n">
+        <v>10</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>46046.5</v>
+      </c>
+      <c r="S40" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T40" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>ORP-R1.0-Q_trend-658a313640a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Q_var</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>risk_var</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.2040077048153092</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.4024378858369875</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.5824132447081269</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.6934581704850538</v>
+      </c>
+      <c r="I41" t="n">
+        <v>465</v>
+      </c>
+      <c r="J41" t="n">
+        <v>97</v>
+      </c>
+      <c r="K41" t="n">
+        <v>24</v>
+      </c>
+      <c r="L41" t="n">
+        <v>10</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>46046.5</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T41" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>ORP-R1.0-Q_var-9bcb67fcbaf1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Q_dist</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>risk_dist</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.31137029780911</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.4227377033176911</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.5618948284441422</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.8218040472452308</v>
+      </c>
+      <c r="I42" t="n">
+        <v>465</v>
+      </c>
+      <c r="J42" t="n">
+        <v>23</v>
+      </c>
+      <c r="K42" t="n">
+        <v>24</v>
+      </c>
+      <c r="L42" t="n">
+        <v>3</v>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>v1.2_high_quality_public_external_D5_gate</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>46046.5</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T42" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>ORP-R0.0-Q_dist-7a1ec31e2292</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Q_dist_w1_candidate</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>risk_dist_w1</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.3426253184510224</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.4897517323509599</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.6599818427110471</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.9854141528161265</v>
+      </c>
+      <c r="I43" t="n">
+        <v>465</v>
+      </c>
+      <c r="J43" t="n">
+        <v>23</v>
+      </c>
+      <c r="K43" t="n">
+        <v>24</v>
+      </c>
+      <c r="L43" t="n">
+        <v>3</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>construct_ablation_only</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>46046.5</v>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T43" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>ORP-R0.0-Q_dist_w1_candidate-0c6b33ac2473</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Q_dist_ks_candidate</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>risk_dist_ks</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.3263888888888889</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.6138888888888888</v>
+      </c>
+      <c r="I44" t="n">
+        <v>465</v>
+      </c>
+      <c r="J44" t="n">
+        <v>23</v>
+      </c>
+      <c r="K44" t="n">
+        <v>24</v>
+      </c>
+      <c r="L44" t="n">
+        <v>3</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>construct_ablation_only</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>46046.5</v>
+      </c>
+      <c r="S44" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T44" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>ORP-R0.0-Q_dist_ks_candidate-607de4e743f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Q_trend</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>risk_trend</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.759905590225795</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.336487910112083</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.08694363935768</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2.872750218451698</v>
+      </c>
+      <c r="I45" t="n">
+        <v>465</v>
+      </c>
+      <c r="J45" t="n">
+        <v>23</v>
+      </c>
+      <c r="K45" t="n">
+        <v>24</v>
+      </c>
+      <c r="L45" t="n">
+        <v>3</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>46046.5</v>
+      </c>
+      <c r="S45" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T45" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>ORP-R0.0-Q_trend-5519749caadb</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Q_var</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>risk_var</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.2040077048153092</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.4024378858369875</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.5824132447081269</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.6934581704850538</v>
+      </c>
+      <c r="I46" t="n">
+        <v>465</v>
+      </c>
+      <c r="J46" t="n">
+        <v>23</v>
+      </c>
+      <c r="K46" t="n">
+        <v>24</v>
+      </c>
+      <c r="L46" t="n">
+        <v>3</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>46046.5</v>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T46" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>ORP-R0.0-Q_var-a111b81afb9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Q_dist</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>risk_dist</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.31137029780911</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.4227377033176911</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.5618948284441422</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.8218040472452308</v>
+      </c>
+      <c r="I47" t="n">
+        <v>465</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>24</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>46046.5</v>
+      </c>
+      <c r="S47" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T47" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>ORP-Rnan-Q_dist-5b8d87b6ea99</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Q_dist_w1_candidate</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>risk_dist_w1</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.3426253184510224</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.4897517323509599</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.6599818427110471</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.9854141528161265</v>
+      </c>
+      <c r="I48" t="n">
+        <v>465</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>24</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>construct_ablation_only</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>46046.5</v>
+      </c>
+      <c r="S48" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T48" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>ORP-Rnan-Q_dist_w1_candidate-8df0e566bc49</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Q_dist_ks_candidate</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>risk_dist_ks</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.3263888888888889</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.6138888888888888</v>
+      </c>
+      <c r="I49" t="n">
+        <v>465</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>24</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>construct_ablation_only</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>46046.5</v>
+      </c>
+      <c r="S49" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T49" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>ORP-Rnan-Q_dist_ks_candidate-fb0ed96f57f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Q_trend</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>risk_trend</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0.759905590225795</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.336487910112083</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2.08694363935768</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2.872750218451698</v>
+      </c>
+      <c r="I50" t="n">
+        <v>465</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>24</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>46046.5</v>
+      </c>
+      <c r="S50" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T50" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>ORP-Rnan-Q_trend-212058677f5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Q_var</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>risk_var</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.2040077048153092</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.4024378858369875</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.5824132447081269</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.6934581704850538</v>
+      </c>
+      <c r="I51" t="n">
+        <v>465</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>24</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>45871.95833333334</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>46046.5</v>
+      </c>
+      <c r="S51" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="T51" s="2" t="n">
+        <v>46046.99998842592</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>development_only_high_quality_common_support_external_D5_gate</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>ORP-Rnan-Q_var-c9c1a5d10dfb</t>
         </is>
       </c>
     </row>
@@ -2519,7 +5725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2543,26 +5749,76 @@
           <t>D5_status</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>fit_period</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>validation_period</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>terminal_status</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>common_support_contract</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>distribution_component_version</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d4-v1.4-canonical-d4-20260726</t>
+          <t>d4-v1.5-common-support-frozen-d4-20260813</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D4CAL-V14-7a16d7f511d3</t>
+          <t>D4CAL-V15-f6c351de01b0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>D4V14_20260726_100717</t>
+          <t>D4V15_20260813_033216</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>pending_not_available</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00 to 2026-01-24 23:59:59</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-02-01 00:00:00 to 2026-04-13 23:59:59</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>pending_genuinely_unseen_future_period</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>synchronous_timestamp_primary</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
     </row>

--- a/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/data/D4_mapping_params.xlsx
+++ b/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/data/D4_mapping_params.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y51"/>
+  <dimension ref="A1:AV51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,65 +498,180 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>variable_independent_blocks</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>min_exact_independent_blocks</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>support_admission_rule</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_reason</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>mapping_scope</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>calibration_quality</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mapping_evidence_quality</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>percentile_precision_grade</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>exact_candidate_percentile_precision_grade</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>percentile_precision_role</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>percentile_precision_bootstrap_repetitions</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>q90_block_CI_low</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>q90_block_CI_high</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>q90_relative_CI_width</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>q97_5_block_CI_low</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>q97_5_block_CI_high</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>q97_5_relative_CI_width</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>percentile_precision_max_relative_CI_width</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>exact_candidate_q90_block_CI_low</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>exact_candidate_q90_block_CI_high</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>exact_candidate_q90_relative_CI_width</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>exact_candidate_q97_5_block_CI_low</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>exact_candidate_q97_5_block_CI_high</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>exact_candidate_q97_5_relative_CI_width</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>exact_candidate_percentile_precision_max_relative_CI_width</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mapping_role</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>fit_phase</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>fit_start</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>fit_end</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>configured_fit_start</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>configured_fit_end</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>common_support_policy</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>distribution_component_version</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>benchmark_source</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mapping_type</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>mapping_id</t>
         </is>
@@ -600,66 +715,147 @@
         <v>1106</v>
       </c>
       <c r="K2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M2" t="n">
+        <v>26</v>
+      </c>
+      <c r="N2" t="n">
         <v>6</v>
       </c>
-      <c r="L2" t="n">
-        <v>6</v>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>admitted_supported_precision</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>600</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.4022133962337249</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.4978168242492307</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.2161982810983553</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.5813326390386387</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8591544676345446</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.3961144860249157</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.3961144860249157</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.4023900734112825</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.5014641887939283</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.224046918522567</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.5774777003355133</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.8630693021836692</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.4071925202956559</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.4071925202956559</v>
+      </c>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="AN2" s="2" t="n">
         <v>45871.91666666666</v>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="AO2" s="2" t="n">
         <v>45912.08333333334</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="AP2" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T2" s="2" t="n">
+      <c r="AQ2" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>DO-R2.0-Q_dist-420c6950886d</t>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>DO-R2.0-Q_dist-b4957d2a5327</t>
         </is>
       </c>
     </row>
@@ -701,66 +897,147 @@
         <v>1106</v>
       </c>
       <c r="K3" t="n">
+        <v>7</v>
+      </c>
+      <c r="L3" t="n">
+        <v>7</v>
+      </c>
+      <c r="M3" t="n">
+        <v>26</v>
+      </c>
+      <c r="N3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" t="n">
-        <v>6</v>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>admitted_supported_precision</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>600</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.498515756232293</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.5970638215721259</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.1874386090731469</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.707321858639005</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.047664853464982</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.3982717014513208</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.3982717014513208</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.5043413828522748</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.5928609718724397</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.1683644279007461</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.7252528084949205</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.047664853464982</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.3772887812316604</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.3772887812316604</v>
+      </c>
+      <c r="AL3" t="inlineStr">
         <is>
           <t>construct_ablation_only</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="n">
+      <c r="AN3" s="2" t="n">
         <v>45871.91666666666</v>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="AO3" s="2" t="n">
         <v>45912.08333333334</v>
       </c>
-      <c r="S3" s="2" t="n">
+      <c r="AP3" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T3" s="2" t="n">
+      <c r="AQ3" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AT3" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>DO-R2.0-Q_dist_w1_candidate-5d2974501d82</t>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>DO-R2.0-Q_dist_w1_candidate-6cbc1449e122</t>
         </is>
       </c>
     </row>
@@ -802,66 +1079,147 @@
         <v>1106</v>
       </c>
       <c r="K4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M4" t="n">
+        <v>26</v>
+      </c>
+      <c r="N4" t="n">
         <v>6</v>
       </c>
-      <c r="L4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>admitted_supported_precision</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>600</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.2777083333333333</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.3729340277777781</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.2980978260869576</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.4382291666666667</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.6014149305555548</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.2960472440944868</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.2980978260869576</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.2708333333333334</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.3702604166666669</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.3112500000000007</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.419444444444445</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.5993055555555552</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.3262992125984235</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.3262992125984235</v>
+      </c>
+      <c r="AL4" t="inlineStr">
         <is>
           <t>construct_ablation_only</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="AN4" s="2" t="n">
         <v>45871.91666666666</v>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="AO4" s="2" t="n">
         <v>45912.08333333334</v>
       </c>
-      <c r="S4" s="2" t="n">
+      <c r="AP4" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T4" s="2" t="n">
+      <c r="AQ4" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="AT4" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AU4" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>DO-R2.0-Q_dist_ks_candidate-2edb3e90b80b</t>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>DO-R2.0-Q_dist_ks_candidate-3245016b54d4</t>
         </is>
       </c>
     </row>
@@ -903,66 +1261,147 @@
         <v>1106</v>
       </c>
       <c r="K5" t="n">
+        <v>7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>26</v>
+      </c>
+      <c r="N5" t="n">
         <v>6</v>
       </c>
-      <c r="L5" t="n">
-        <v>6</v>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>admitted_supported_precision</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>600</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.300723459732291</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.575793152836593</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.1915762739969241</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.595213511026788</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.148272443407849</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.2906824037140296</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.2906824037140296</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.300849282571903</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.579573673139638</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.1941216410082038</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.667387377653714</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2.158250946229074</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.2579931245208077</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.2579931245208077</v>
+      </c>
+      <c r="AL5" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="AN5" s="2" t="n">
         <v>45871.91666666666</v>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="AO5" s="2" t="n">
         <v>45912.08333333334</v>
       </c>
-      <c r="S5" s="2" t="n">
+      <c r="AP5" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T5" s="2" t="n">
+      <c r="AQ5" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AU5" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>DO-R2.0-Q_trend-b84f1267d372</t>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>DO-R2.0-Q_trend-1caba1313460</t>
         </is>
       </c>
     </row>
@@ -1004,66 +1443,147 @@
         <v>1106</v>
       </c>
       <c r="K6" t="n">
+        <v>7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>26</v>
+      </c>
+      <c r="N6" t="n">
         <v>6</v>
       </c>
-      <c r="L6" t="n">
-        <v>6</v>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>admitted_supported_precision</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>wide_interval</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>600</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.2851532869556176</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.46324349747652</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.4996858552529903</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.5372040927711834</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.265424843483066</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.966826088206295</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.966826088206295</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.2875616884487753</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.4895734682137412</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.5668050402533952</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.5146734695130175</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.270809083588593</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.003887402543121</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.003887402543121</v>
+      </c>
+      <c r="AL6" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="AN6" s="2" t="n">
         <v>45871.91666666666</v>
       </c>
-      <c r="R6" s="2" t="n">
+      <c r="AO6" s="2" t="n">
         <v>45912.08333333334</v>
       </c>
-      <c r="S6" s="2" t="n">
+      <c r="AP6" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T6" s="2" t="n">
+      <c r="AQ6" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="AT6" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="AU6" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>DO-R2.0-Q_var-c3b49167d4c9</t>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>DO-R2.0-Q_var-e2084f3ad6b0</t>
         </is>
       </c>
     </row>
@@ -1105,66 +1625,147 @@
         <v>524</v>
       </c>
       <c r="K7" t="n">
+        <v>7</v>
+      </c>
+      <c r="L7" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" t="n">
+        <v>26</v>
+      </c>
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="L7" t="n">
-        <v>6</v>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>admitted_supported_precision</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>600</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.7671639098763812</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.007945833658847</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.2709690221216742</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.006753954742556</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.403189382894152</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.3530853547398707</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.3530853547398707</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.7755020270644992</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.9937348117799383</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.2455928723397738</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.012064053448866</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.39283570949073</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.339134410552778</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.339134410552778</v>
+      </c>
+      <c r="AL7" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="AN7" s="2" t="n">
         <v>45914.125</v>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="AO7" s="2" t="n">
         <v>45955.70833333334</v>
       </c>
-      <c r="S7" s="2" t="n">
+      <c r="AP7" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T7" s="2" t="n">
+      <c r="AQ7" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AT7" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AU7" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>DO-R3.0-Q_dist-80297c6b6abe</t>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>DO-R3.0-Q_dist-76febe8f8827</t>
         </is>
       </c>
     </row>
@@ -1206,66 +1807,147 @@
         <v>524</v>
       </c>
       <c r="K8" t="n">
+        <v>7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" t="n">
+        <v>26</v>
+      </c>
+      <c r="N8" t="n">
         <v>6</v>
       </c>
-      <c r="L8" t="n">
-        <v>6</v>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>admitted_supported_precision</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>600</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.897864935460327</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.285035144783718</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.350935428298538</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.262607980860614</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.841930759309609</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.4057099119109272</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.4057099119109272</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.9209236737645321</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.259881311439644</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.3072350115998181</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.287937625064222</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.798244701003069</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.3573770038543381</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.3573770038543381</v>
+      </c>
+      <c r="AL8" t="inlineStr">
         <is>
           <t>construct_ablation_only</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="n">
+      <c r="AN8" s="2" t="n">
         <v>45914.125</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="AO8" s="2" t="n">
         <v>45955.70833333334</v>
       </c>
-      <c r="S8" s="2" t="n">
+      <c r="AP8" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T8" s="2" t="n">
+      <c r="AQ8" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AT8" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AU8" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>DO-R3.0-Q_dist_w1_candidate-447872a6342c</t>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>DO-R3.0-Q_dist_w1_candidate-b3fafa46c4df</t>
         </is>
       </c>
     </row>
@@ -1307,66 +1989,147 @@
         <v>524</v>
       </c>
       <c r="K9" t="n">
+        <v>7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>26</v>
+      </c>
+      <c r="N9" t="n">
         <v>6</v>
       </c>
-      <c r="L9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>admitted_supported_precision</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>600</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.5428472222222221</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.6597222222222223</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.1934482758620693</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.6502343749999993</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8211935763888889</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.232246462264152</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.232246462264152</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.5347222222222222</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.6597222222222223</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.2068965517241381</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.638888888888889</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.826388888888889</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.2547169811320755</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.2547169811320755</v>
+      </c>
+      <c r="AL9" t="inlineStr">
         <is>
           <t>construct_ablation_only</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="n">
+      <c r="AN9" s="2" t="n">
         <v>45914.125</v>
       </c>
-      <c r="R9" s="2" t="n">
+      <c r="AO9" s="2" t="n">
         <v>45955.70833333334</v>
       </c>
-      <c r="S9" s="2" t="n">
+      <c r="AP9" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T9" s="2" t="n">
+      <c r="AQ9" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AT9" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AU9" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>DO-R3.0-Q_dist_ks_candidate-07a99340fe92</t>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>DO-R3.0-Q_dist_ks_candidate-55623b6f6cd2</t>
         </is>
       </c>
     </row>
@@ -1408,66 +2171,147 @@
         <v>524</v>
       </c>
       <c r="K10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>26</v>
+      </c>
+      <c r="N10" t="n">
         <v>6</v>
       </c>
-      <c r="L10" t="n">
-        <v>6</v>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>admitted_supported_precision</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>600</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.133246874254896</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.614159890343398</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.2107867407076542</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.058206598260309</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.433359186221359</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.1138503223854833</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.2107867407076542</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.153438251873499</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.617921162627738</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.2035853378821265</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>3.057075504097719</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>3.484480449054474</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.1297077304915953</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.2035853378821265</v>
+      </c>
+      <c r="AL10" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="n">
+      <c r="AN10" s="2" t="n">
         <v>45914.125</v>
       </c>
-      <c r="R10" s="2" t="n">
+      <c r="AO10" s="2" t="n">
         <v>45955.70833333334</v>
       </c>
-      <c r="S10" s="2" t="n">
+      <c r="AP10" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T10" s="2" t="n">
+      <c r="AQ10" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AT10" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="AU10" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>DO-R3.0-Q_trend-27029d7092e4</t>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>DO-R3.0-Q_trend-9cb0a4886921</t>
         </is>
       </c>
     </row>
@@ -1509,66 +2353,147 @@
         <v>524</v>
       </c>
       <c r="K11" t="n">
+        <v>7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M11" t="n">
+        <v>26</v>
+      </c>
+      <c r="N11" t="n">
         <v>6</v>
       </c>
-      <c r="L11" t="n">
-        <v>6</v>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>admitted_supported_precision</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>600</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.8020691030903181</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.021968076236787</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.2293139113590516</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.018739861986783</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.47726812602964</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.3849034826161544</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.3849034826161544</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.8300245084900122</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.023739863829068</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.202009246280197</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.021546191732043</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.47775882236145</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.3829596648949947</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.3829596648949947</v>
+      </c>
+      <c r="AL11" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="n">
+      <c r="AN11" s="2" t="n">
         <v>45914.125</v>
       </c>
-      <c r="R11" s="2" t="n">
+      <c r="AO11" s="2" t="n">
         <v>45955.70833333334</v>
       </c>
-      <c r="S11" s="2" t="n">
+      <c r="AP11" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T11" s="2" t="n">
+      <c r="AQ11" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="AT11" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="AU11" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>DO-R3.0-Q_var-1708a867e09c</t>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>DO-R3.0-Q_var-fa3fb78f3123</t>
         </is>
       </c>
     </row>
@@ -1610,66 +2535,147 @@
         <v>732</v>
       </c>
       <c r="K12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L12" t="n">
-        <v>11</v>
-      </c>
-      <c r="M12" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="M12" t="n">
+        <v>26</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>admitted_supported_precision</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>600</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.3986250648975326</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.4865989398763853</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.1964291371924452</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.5133137727859546</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.7722771075462395</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.4240475885297668</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.4240475885297668</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.3999027488020895</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.4992178591905886</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.221751985444256</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.509055970193074</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.7722771075462395</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.4310196601692446</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.4310196601692446</v>
+      </c>
+      <c r="AL12" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="n">
+      <c r="AN12" s="2" t="n">
         <v>45946.91666666666</v>
       </c>
-      <c r="R12" s="2" t="n">
+      <c r="AO12" s="2" t="n">
         <v>46023.91666666666</v>
       </c>
-      <c r="S12" s="2" t="n">
+      <c r="AP12" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T12" s="2" t="n">
+      <c r="AQ12" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="AT12" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="AU12" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>DO-R1.0-Q_dist-07fec55c78e8</t>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>DO-R1.0-Q_dist-4f51619c13df</t>
         </is>
       </c>
     </row>
@@ -1711,66 +2717,147 @@
         <v>732</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L13" t="n">
-        <v>11</v>
-      </c>
-      <c r="M13" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="M13" t="n">
+        <v>26</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>admitted_supported_precision</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>600</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.4550023556148327</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.568833604937601</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.2134140578420884</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.604004707245082</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8890969575633081</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.4163852246536552</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.4163852246536552</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.4547942863621648</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.5720594260632041</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.2198520130096868</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.5982735229275166</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.8890969575633081</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.4247557800333166</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.4247557800333166</v>
+      </c>
+      <c r="AL13" t="inlineStr">
         <is>
           <t>construct_ablation_only</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="AM13" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="n">
+      <c r="AN13" s="2" t="n">
         <v>45946.91666666666</v>
       </c>
-      <c r="R13" s="2" t="n">
+      <c r="AO13" s="2" t="n">
         <v>46023.91666666666</v>
       </c>
-      <c r="S13" s="2" t="n">
+      <c r="AP13" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T13" s="2" t="n">
+      <c r="AQ13" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="AR13" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="AS13" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="AT13" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="AU13" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>DO-R1.0-Q_dist_w1_candidate-4d9a797bee8f</t>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>DO-R1.0-Q_dist_w1_candidate-43a79b8c9634</t>
         </is>
       </c>
     </row>
@@ -1812,66 +2899,147 @@
         <v>732</v>
       </c>
       <c r="K14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L14" t="n">
-        <v>11</v>
-      </c>
-      <c r="M14" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="M14" t="n">
+        <v>26</v>
+      </c>
+      <c r="N14" t="n">
+        <v>6</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>admitted_supported_precision</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>600</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.3263888888888888</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.370902777777778</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.130816326530613</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.4097222222222223</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.6388888888888888</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.4714285714285713</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.4714285714285713</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.3263888888888888</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.3680555555555556</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.122448979591837</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.4117534722222219</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.6293229166666658</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.4475714285714275</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.4475714285714275</v>
+      </c>
+      <c r="AL14" t="inlineStr">
         <is>
           <t>construct_ablation_only</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="AM14" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="n">
+      <c r="AN14" s="2" t="n">
         <v>45946.91666666666</v>
       </c>
-      <c r="R14" s="2" t="n">
+      <c r="AO14" s="2" t="n">
         <v>46023.91666666666</v>
       </c>
-      <c r="S14" s="2" t="n">
+      <c r="AP14" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T14" s="2" t="n">
+      <c r="AQ14" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="AR14" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="AS14" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="AT14" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="AU14" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>DO-R1.0-Q_dist_ks_candidate-09bf2c99beb2</t>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>DO-R1.0-Q_dist_ks_candidate-ac6eba37eaf8</t>
         </is>
       </c>
     </row>
@@ -1913,66 +3081,147 @@
         <v>732</v>
       </c>
       <c r="K15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L15" t="n">
-        <v>11</v>
-      </c>
-      <c r="M15" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="M15" t="n">
+        <v>26</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>admitted_supported_precision</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>600</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.489865751022409</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.726218181181395</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.1450019739441193</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.025465176891017</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.461072437211405</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.1904376695346459</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.1904376695346459</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.503085041561415</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.726218181181395</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.1368919527312747</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2.031229324963237</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>2.461072437211405</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.1879177140019516</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.1879177140019516</v>
+      </c>
+      <c r="AL15" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="AM15" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="n">
+      <c r="AN15" s="2" t="n">
         <v>45946.91666666666</v>
       </c>
-      <c r="R15" s="2" t="n">
+      <c r="AO15" s="2" t="n">
         <v>46023.91666666666</v>
       </c>
-      <c r="S15" s="2" t="n">
+      <c r="AP15" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T15" s="2" t="n">
+      <c r="AQ15" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="AR15" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="AS15" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="AT15" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="AU15" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>DO-R1.0-Q_trend-dcdbf54f940a</t>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>DO-R1.0-Q_trend-2863961f4354</t>
         </is>
       </c>
     </row>
@@ -2014,66 +3263,147 @@
         <v>732</v>
       </c>
       <c r="K16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L16" t="n">
-        <v>11</v>
-      </c>
-      <c r="M16" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="M16" t="n">
+        <v>26</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>admitted_supported_precision</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>600</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.3154072232492623</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4208566397177234</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.2741176602175826</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.4652003362034388</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8015237996025506</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.5848373428639897</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.5848373428639897</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.3141902903030904</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.4206557485484986</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.2767588791442266</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.4484113261658254</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.8015237996025506</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.6140319756751497</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.6140319756751497</v>
+      </c>
+      <c r="AL16" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="AM16" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="n">
+      <c r="AN16" s="2" t="n">
         <v>45946.91666666666</v>
       </c>
-      <c r="R16" s="2" t="n">
+      <c r="AO16" s="2" t="n">
         <v>46023.91666666666</v>
       </c>
-      <c r="S16" s="2" t="n">
+      <c r="AP16" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T16" s="2" t="n">
+      <c r="AQ16" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="AR16" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="AS16" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="AT16" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="AU16" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>DO-R1.0-Q_var-7f5460ae7a39</t>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>DO-R1.0-Q_var-02b65795d04e</t>
         </is>
       </c>
     </row>
@@ -2115,66 +3445,147 @@
         <v>569</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L17" t="n">
-        <v>5</v>
-      </c>
-      <c r="M17" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M17" t="n">
+        <v>26</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>admitted_minimum_support_tail_precision_wide</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>wide_interval</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>wide_interval</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>600</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.3473391782735709</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.8099696483211665</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.085141244541083</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.4269912540262203</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.454120104953655</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.290989916520985</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.290989916520985</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.3475195245010317</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.8099696483211665</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.084718226295668</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.4209755687847131</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.454120104953655</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.298550982477547</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.298550982477547</v>
+      </c>
+      <c r="AL17" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="AM17" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="n">
+      <c r="AN17" s="2" t="n">
         <v>46012</v>
       </c>
-      <c r="R17" s="2" t="n">
+      <c r="AO17" s="2" t="n">
         <v>46046.95833333334</v>
       </c>
-      <c r="S17" s="2" t="n">
+      <c r="AP17" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T17" s="2" t="n">
+      <c r="AQ17" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="AR17" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="AS17" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="AT17" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="AU17" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>DO-R0.0-Q_dist-ca8755d8a837</t>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>DO-R0.0-Q_dist-1149a3e04afc</t>
         </is>
       </c>
     </row>
@@ -2216,66 +3627,147 @@
         <v>569</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
-      </c>
-      <c r="M18" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M18" t="n">
+        <v>26</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>admitted_minimum_support_tail_precision_wide</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>wide_interval</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>wide_interval</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>600</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.3893122289628665</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.9927472919897208</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.196466443981116</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.469618774988825</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.858718693441277</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.388084934486865</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.388084934486865</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.3893127446892111</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.9927472919897208</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.196465421419943</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.4695839105469484</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.858718693441277</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.38811977345408</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.38811977345408</v>
+      </c>
+      <c r="AL18" t="inlineStr">
         <is>
           <t>construct_ablation_only</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="AM18" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="n">
+      <c r="AN18" s="2" t="n">
         <v>46012</v>
       </c>
-      <c r="R18" s="2" t="n">
+      <c r="AO18" s="2" t="n">
         <v>46046.95833333334</v>
       </c>
-      <c r="S18" s="2" t="n">
+      <c r="AP18" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T18" s="2" t="n">
+      <c r="AQ18" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="AR18" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="AS18" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="AT18" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="AU18" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>DO-R0.0-Q_dist_w1_candidate-b772003c9988</t>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>DO-R0.0-Q_dist_w1_candidate-c15e66056ae0</t>
         </is>
       </c>
     </row>
@@ -2317,66 +3809,147 @@
         <v>569</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
-      </c>
-      <c r="M19" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M19" t="n">
+        <v>26</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>admitted_supported_precision</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>600</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.2916666666666666</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.5271006944444446</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.6780500000000007</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.3472222222222223</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.8771929824561406</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8771929824561406</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.5348958333333332</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.7004999999999997</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.3472222222222222</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.8771929824561407</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.8771929824561407</v>
+      </c>
+      <c r="AL19" t="inlineStr">
         <is>
           <t>construct_ablation_only</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="AM19" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="n">
+      <c r="AN19" s="2" t="n">
         <v>46012</v>
       </c>
-      <c r="R19" s="2" t="n">
+      <c r="AO19" s="2" t="n">
         <v>46046.95833333334</v>
       </c>
-      <c r="S19" s="2" t="n">
+      <c r="AP19" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T19" s="2" t="n">
+      <c r="AQ19" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="AR19" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="AS19" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="AT19" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="AU19" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>DO-R0.0-Q_dist_ks_candidate-10ca77d0be6d</t>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>DO-R0.0-Q_dist_ks_candidate-cbcd60804aa1</t>
         </is>
       </c>
     </row>
@@ -2418,66 +3991,147 @@
         <v>569</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M20" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>26</v>
+      </c>
+      <c r="N20" t="n">
+        <v>6</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>admitted_supported_precision</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>600</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.448197002198498</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.3970761662605</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.5841150908881426</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.910470243316915</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.97518161500475</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.428907011201884</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.5841150908881426</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.44271107389094</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.430957151183649</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.6083487435708537</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.908765586294288</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2.944915809374936</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.4174014734464432</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.6083487435708537</v>
+      </c>
+      <c r="AL20" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="AM20" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="n">
+      <c r="AN20" s="2" t="n">
         <v>46012</v>
       </c>
-      <c r="R20" s="2" t="n">
+      <c r="AO20" s="2" t="n">
         <v>46046.95833333334</v>
       </c>
-      <c r="S20" s="2" t="n">
+      <c r="AP20" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T20" s="2" t="n">
+      <c r="AQ20" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="AR20" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="AS20" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="AT20" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="AU20" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>DO-R0.0-Q_trend-ae24d055f465</t>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>DO-R0.0-Q_trend-4bfe66af19f7</t>
         </is>
       </c>
     </row>
@@ -2519,66 +4173,147 @@
         <v>569</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>5</v>
-      </c>
-      <c r="M21" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M21" t="n">
+        <v>26</v>
+      </c>
+      <c r="N21" t="n">
+        <v>6</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>admitted_minimum_support_tail_precision_wide</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>wide_interval</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>wide_interval</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
+        <v>600</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.3274226527213424</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.5582827969944223</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.5258245671599272</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.4971075215732831</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.264771956110769</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.18747616170696</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.18747616170696</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.3248911331236954</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.5582827969944223</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.5315905481216084</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.4971037378633381</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.264771956110769</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.187482014609817</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.187482014609817</v>
+      </c>
+      <c r="AL21" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="AM21" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q21" s="2" t="n">
+      <c r="AN21" s="2" t="n">
         <v>46012</v>
       </c>
-      <c r="R21" s="2" t="n">
+      <c r="AO21" s="2" t="n">
         <v>46046.95833333334</v>
       </c>
-      <c r="S21" s="2" t="n">
+      <c r="AP21" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T21" s="2" t="n">
+      <c r="AQ21" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="AR21" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="AS21" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="AT21" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="AU21" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>DO-R0.0-Q_var-c56483782a79</t>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>DO-R0.0-Q_var-cb47098c5ae0</t>
         </is>
       </c>
     </row>
@@ -2623,61 +4358,128 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M22" t="n">
+        <v>26</v>
+      </c>
+      <c r="N22" t="n">
+        <v>6</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>exact_windows=0&lt;100; exact_independent_blocks=0&lt;6</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>insufficient_independent_support</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W22" t="n">
+        <v>600</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.4717263392784439</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.7056246870057866</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.4059292306288544</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.7270271716279728</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.018793420254878</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.3281008087088189</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.4059292306288544</v>
+      </c>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="AM22" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="n">
+      <c r="AN22" s="2" t="n">
         <v>45871.91666666666</v>
       </c>
-      <c r="R22" s="2" t="n">
+      <c r="AO22" s="2" t="n">
         <v>46046.95833333334</v>
       </c>
-      <c r="S22" s="2" t="n">
+      <c r="AP22" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T22" s="2" t="n">
+      <c r="AQ22" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="AR22" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="AS22" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="AT22" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="AU22" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>DO-Rnan-Q_dist-759f7f0cb608</t>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>DO-Rnan-Q_dist-5cff344f15f3</t>
         </is>
       </c>
     </row>
@@ -2722,61 +4524,128 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M23" t="n">
+        <v>26</v>
+      </c>
+      <c r="N23" t="n">
+        <v>6</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>exact_windows=0&lt;100; exact_independent_blocks=0&lt;6</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>insufficient_independent_support</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W23" t="n">
+        <v>600</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.552023638743236</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.8427652347013044</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.4198548759930235</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.8552262307776529</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.310280181274406</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.4165185389508039</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.4198548759930235</v>
+      </c>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr">
         <is>
           <t>construct_ablation_only</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="AM23" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="n">
+      <c r="AN23" s="2" t="n">
         <v>45871.91666666666</v>
       </c>
-      <c r="R23" s="2" t="n">
+      <c r="AO23" s="2" t="n">
         <v>46046.95833333334</v>
       </c>
-      <c r="S23" s="2" t="n">
+      <c r="AP23" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T23" s="2" t="n">
+      <c r="AQ23" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="AR23" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="AS23" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="AT23" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="AU23" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>DO-Rnan-Q_dist_w1_candidate-a59ac067fc51</t>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>DO-Rnan-Q_dist_w1_candidate-6d86703503e2</t>
         </is>
       </c>
     </row>
@@ -2821,61 +4690,128 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M24" t="n">
+        <v>26</v>
+      </c>
+      <c r="N24" t="n">
+        <v>6</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>exact_windows=0&lt;100; exact_independent_blocks=0&lt;6</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>insufficient_independent_support</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>600</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.3472222222222222</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.513888888888889</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.3809523809523813</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.6736111111111112</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.1931818181818182</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.3809523809523813</v>
+      </c>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr">
         <is>
           <t>construct_ablation_only</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="AM24" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q24" s="2" t="n">
+      <c r="AN24" s="2" t="n">
         <v>45871.91666666666</v>
       </c>
-      <c r="R24" s="2" t="n">
+      <c r="AO24" s="2" t="n">
         <v>46046.95833333334</v>
       </c>
-      <c r="S24" s="2" t="n">
+      <c r="AP24" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T24" s="2" t="n">
+      <c r="AQ24" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="AR24" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="AS24" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="AT24" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="AU24" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>DO-Rnan-Q_dist_ks_candidate-477ff8d7f9ee</t>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>DO-Rnan-Q_dist_ks_candidate-28b45fcc0f3e</t>
         </is>
       </c>
     </row>
@@ -2920,61 +4856,128 @@
       <c r="L25" t="n">
         <v>0</v>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M25" t="n">
+        <v>26</v>
+      </c>
+      <c r="N25" t="n">
+        <v>6</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>exact_windows=0&lt;100; exact_independent_blocks=0&lt;6</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>insufficient_independent_support</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W25" t="n">
+        <v>600</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.543978312751308</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.894047427298448</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.2095211407626745</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.20859522349249</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.836687846963085</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.2520684797604136</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.2520684797604136</v>
+      </c>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="AM25" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="n">
+      <c r="AN25" s="2" t="n">
         <v>45871.91666666666</v>
       </c>
-      <c r="R25" s="2" t="n">
+      <c r="AO25" s="2" t="n">
         <v>46046.95833333334</v>
       </c>
-      <c r="S25" s="2" t="n">
+      <c r="AP25" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T25" s="2" t="n">
+      <c r="AQ25" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="AR25" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="AS25" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="AT25" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="AU25" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>DO-Rnan-Q_trend-8290f3c9ad42</t>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>DO-Rnan-Q_trend-4bb1a2503759</t>
         </is>
       </c>
     </row>
@@ -3019,61 +5022,128 @@
       <c r="L26" t="n">
         <v>0</v>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M26" t="n">
+        <v>26</v>
+      </c>
+      <c r="N26" t="n">
+        <v>6</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>exact_windows=0&lt;100; exact_independent_blocks=0&lt;6</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>insufficient_independent_support</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W26" t="n">
+        <v>600</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.4021403307779882</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.7603559106898653</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.6509147711999493</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.7624918722206171</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.102992061099124</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.3579105651304714</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.6509147711999493</v>
+      </c>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="AM26" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="n">
+      <c r="AN26" s="2" t="n">
         <v>45871.91666666666</v>
       </c>
-      <c r="R26" s="2" t="n">
+      <c r="AO26" s="2" t="n">
         <v>46046.95833333334</v>
       </c>
-      <c r="S26" s="2" t="n">
+      <c r="AP26" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T26" s="2" t="n">
+      <c r="AQ26" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="AR26" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="AS26" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="AT26" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="AU26" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>DO-Rnan-Q_var-4c3b3f69641b</t>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>DO-Rnan-Q_var-af491ee0a8a4</t>
         </is>
       </c>
     </row>
@@ -3120,61 +5190,142 @@
       <c r="L27" t="n">
         <v>6</v>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M27" t="n">
+        <v>25</v>
+      </c>
+      <c r="N27" t="n">
+        <v>6</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>admitted_supported_precision</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W27" t="n">
+        <v>600</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.4557010198902735</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.7004346668714444</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.5034574294959816</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.5087306866044045</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.065279266877901</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.6397490495266339</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.6397490495266339</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0.4463429122119312</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.7004346668714444</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.5227085986539654</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0.4958104274291519</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1.065279266877901</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0.654600805186389</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0.654600805186389</v>
+      </c>
+      <c r="AL27" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="AM27" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q27" s="2" t="n">
+      <c r="AN27" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R27" s="2" t="n">
+      <c r="AO27" s="2" t="n">
         <v>45911.41666666666</v>
       </c>
-      <c r="S27" s="2" t="n">
+      <c r="AP27" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T27" s="2" t="n">
+      <c r="AQ27" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="AR27" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="AS27" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="AT27" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="AU27" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>ORP-R2.0-Q_dist-e53b83b86f17</t>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>ORP-R2.0-Q_dist-7782abfdedad</t>
         </is>
       </c>
     </row>
@@ -3221,61 +5372,142 @@
       <c r="L28" t="n">
         <v>6</v>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M28" t="n">
+        <v>25</v>
+      </c>
+      <c r="N28" t="n">
+        <v>6</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>admitted_supported_precision</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W28" t="n">
+        <v>600</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.5465134132218661</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.8431617990856252</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.4856642504802494</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.6169979440448802</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.233798778129835</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.5988320522197518</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.5988320522197518</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0.5460196023921424</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.8795245532092495</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.5460047641871577</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0.6214115829349341</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1.233798778129835</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0.5945469924594016</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0.5945469924594016</v>
+      </c>
+      <c r="AL28" t="inlineStr">
         <is>
           <t>construct_ablation_only</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="AM28" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="n">
+      <c r="AN28" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R28" s="2" t="n">
+      <c r="AO28" s="2" t="n">
         <v>45911.41666666666</v>
       </c>
-      <c r="S28" s="2" t="n">
+      <c r="AP28" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T28" s="2" t="n">
+      <c r="AQ28" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="AR28" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="AS28" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="AT28" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="AU28" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>ORP-R2.0-Q_dist_w1_candidate-822073356f41</t>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>ORP-R2.0-Q_dist_w1_candidate-3fbf2c3ea6f0</t>
         </is>
       </c>
     </row>
@@ -3322,61 +5554,142 @@
       <c r="L29" t="n">
         <v>6</v>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M29" t="n">
+        <v>25</v>
+      </c>
+      <c r="N29" t="n">
+        <v>6</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>admitted_supported_precision</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W29" t="n">
+        <v>600</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.2847222222222222</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.4930555555555556</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.488599348534202</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.3819053819444445</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.8055555555555556</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.672608875413451</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.672608875413451</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.2847222222222222</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.4930555555555556</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.488599348534202</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.3715277777777778</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.8055555555555556</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.6890848952590961</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.6890848952590961</v>
+      </c>
+      <c r="AL29" t="inlineStr">
         <is>
           <t>construct_ablation_only</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="AM29" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="n">
+      <c r="AN29" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R29" s="2" t="n">
+      <c r="AO29" s="2" t="n">
         <v>45911.41666666666</v>
       </c>
-      <c r="S29" s="2" t="n">
+      <c r="AP29" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T29" s="2" t="n">
+      <c r="AQ29" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="AR29" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="AS29" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="AT29" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="AU29" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>ORP-R2.0-Q_dist_ks_candidate-ece56f157b83</t>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>ORP-R2.0-Q_dist_ks_candidate-41b8f8c49706</t>
         </is>
       </c>
     </row>
@@ -3423,61 +5736,142 @@
       <c r="L30" t="n">
         <v>6</v>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M30" t="n">
+        <v>25</v>
+      </c>
+      <c r="N30" t="n">
+        <v>6</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>admitted_supported_precision</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W30" t="n">
+        <v>600</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.236085307960562</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.835763998861828</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.359562120286755</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.674178394213148</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.448415601294599</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.3558254127006438</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.359562120286755</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.240175302551528</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.835763998861828</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.3571097951509745</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.674178394213148</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>2.445382028224638</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.3544312374017773</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0.3571097951509745</v>
+      </c>
+      <c r="AL30" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="AM30" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q30" s="2" t="n">
+      <c r="AN30" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R30" s="2" t="n">
+      <c r="AO30" s="2" t="n">
         <v>45911.41666666666</v>
       </c>
-      <c r="S30" s="2" t="n">
+      <c r="AP30" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T30" s="2" t="n">
+      <c r="AQ30" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="AR30" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="AS30" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="AT30" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="AU30" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>ORP-R2.0-Q_trend-b5bbfa0475dd</t>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>ORP-R2.0-Q_trend-f1afcfc946cf</t>
         </is>
       </c>
     </row>
@@ -3524,61 +5918,142 @@
       <c r="L31" t="n">
         <v>6</v>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M31" t="n">
+        <v>25</v>
+      </c>
+      <c r="N31" t="n">
+        <v>6</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
         <is>
           <t>variable_regime_public</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>adequate</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>admitted_minimum_support_tail_precision_wide</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>wide_interval</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>wide_interval</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W31" t="n">
+        <v>600</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.4033548577010411</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.6356574057956034</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.4293764498132623</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.5535558305679993</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.581630935614005</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.471635554879183</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.471635554879183</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.4031463249072871</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.6405470788801939</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.4387997194175613</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.555356130888318</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1.581630935614005</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.469058519458485</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.469058519458485</v>
+      </c>
+      <c r="AL31" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="AM31" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="n">
+      <c r="AN31" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R31" s="2" t="n">
+      <c r="AO31" s="2" t="n">
         <v>45911.41666666666</v>
       </c>
-      <c r="S31" s="2" t="n">
+      <c r="AP31" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T31" s="2" t="n">
+      <c r="AQ31" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="AR31" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="AS31" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="AT31" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="AU31" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>ORP-R2.0-Q_var-9a9531abce4c</t>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>ORP-R2.0-Q_var-7c38bbeb9259</t>
         </is>
       </c>
     </row>
@@ -3620,66 +6095,147 @@
         <v>98</v>
       </c>
       <c r="K32" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L32" t="n">
         <v>6</v>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M32" t="n">
+        <v>25</v>
+      </c>
+      <c r="N32" t="n">
+        <v>6</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>exact_windows=98&lt;100</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W32" t="n">
+        <v>600</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.4851554002140704</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0.6273442170244999</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.2530523678321494</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.6232170358354469</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.9747618855320392</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0.4277721080530156</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.4277721080530156</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.5298803604074145</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.6420622122345384</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.1800798042753962</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.6288429549126318</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1.003536150204092</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.4841375779554868</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.4841375779554868</v>
+      </c>
+      <c r="AL32" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="AM32" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="n">
+      <c r="AN32" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R32" s="2" t="n">
+      <c r="AO32" s="2" t="n">
         <v>46046.5</v>
       </c>
-      <c r="S32" s="2" t="n">
+      <c r="AP32" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T32" s="2" t="n">
+      <c r="AQ32" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="AR32" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="AS32" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="AT32" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="AU32" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>ORP-R3.0-Q_dist-0811e8f4a3fc</t>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>ORP-R3.0-Q_dist-c5e2bf7d6e21</t>
         </is>
       </c>
     </row>
@@ -3721,66 +6277,147 @@
         <v>98</v>
       </c>
       <c r="K33" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L33" t="n">
         <v>6</v>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M33" t="n">
+        <v>25</v>
+      </c>
+      <c r="N33" t="n">
+        <v>6</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>exact_windows=98&lt;100</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W33" t="n">
+        <v>600</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.6019820641824389</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0.7514299677490757</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.2264424471933055</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.7359892344905878</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.116064680189955</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.3857012248232717</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.3857012248232717</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.6429786048468782</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.7661843514104195</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.1706263722631293</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0.7151972722262385</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1.213352242331477</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.5595697728048674</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0.5595697728048674</v>
+      </c>
+      <c r="AL33" t="inlineStr">
         <is>
           <t>construct_ablation_only</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="AM33" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="n">
+      <c r="AN33" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R33" s="2" t="n">
+      <c r="AO33" s="2" t="n">
         <v>46046.5</v>
       </c>
-      <c r="S33" s="2" t="n">
+      <c r="AP33" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T33" s="2" t="n">
+      <c r="AQ33" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="AR33" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="AS33" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="AT33" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="AU33" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>ORP-R3.0-Q_dist_w1_candidate-ee60a528da46</t>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>ORP-R3.0-Q_dist_w1_candidate-25dc7bb7cceb</t>
         </is>
       </c>
     </row>
@@ -3822,66 +6459,147 @@
         <v>98</v>
       </c>
       <c r="K34" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L34" t="n">
         <v>6</v>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M34" t="n">
+        <v>25</v>
+      </c>
+      <c r="N34" t="n">
+        <v>6</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>exact_windows=98&lt;100</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W34" t="n">
+        <v>600</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.3756770833333335</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.2365476190476187</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.4721267361111112</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.7259505208333314</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.413468608597282</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.413468608597282</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0.3680555555555556</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.4993055555555556</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.2795857988165681</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0.4452907986111108</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0.6874999999999997</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.4040327251665217</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0.4040327251665217</v>
+      </c>
+      <c r="AL34" t="inlineStr">
         <is>
           <t>construct_ablation_only</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="AM34" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="n">
+      <c r="AN34" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R34" s="2" t="n">
+      <c r="AO34" s="2" t="n">
         <v>46046.5</v>
       </c>
-      <c r="S34" s="2" t="n">
+      <c r="AP34" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T34" s="2" t="n">
+      <c r="AQ34" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="AR34" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="AS34" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="AT34" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="AU34" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>ORP-R3.0-Q_dist_ks_candidate-9a3be7cda4d0</t>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>ORP-R3.0-Q_dist_ks_candidate-4527f035f97b</t>
         </is>
       </c>
     </row>
@@ -3923,66 +6641,147 @@
         <v>98</v>
       </c>
       <c r="K35" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L35" t="n">
         <v>6</v>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M35" t="n">
+        <v>25</v>
+      </c>
+      <c r="N35" t="n">
+        <v>6</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>exact_windows=98&lt;100</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W35" t="n">
+        <v>600</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.663538547446298</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>2.559859241596214</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.4294896504372228</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.360852404801319</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>3.180402939033199</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.2852842996818521</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.4294896504372228</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.75543398596329</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.607529165178653</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.3652156915890341</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>2.355801995474923</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>3.435957542278677</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.3916381199857949</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0.3916381199857949</v>
+      </c>
+      <c r="AL35" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="AM35" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="n">
+      <c r="AN35" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R35" s="2" t="n">
+      <c r="AO35" s="2" t="n">
         <v>46046.5</v>
       </c>
-      <c r="S35" s="2" t="n">
+      <c r="AP35" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T35" s="2" t="n">
+      <c r="AQ35" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="AR35" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="AS35" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="AT35" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="AU35" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>ORP-R3.0-Q_trend-5ae5e101f465</t>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>ORP-R3.0-Q_trend-504f4b129289</t>
         </is>
       </c>
     </row>
@@ -4024,66 +6823,147 @@
         <v>98</v>
       </c>
       <c r="K36" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L36" t="n">
         <v>6</v>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M36" t="n">
+        <v>25</v>
+      </c>
+      <c r="N36" t="n">
+        <v>6</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>exact_windows=98&lt;100</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W36" t="n">
+        <v>600</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.4766575985597284</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.6228973654926347</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.2510927906630858</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.6443141628666356</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.7394951295052982</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.1372555269946366</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.2510927906630858</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.4308355616151245</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.6587543612989276</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.4054455361821754</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0.6121061790288984</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.8734536917756317</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0.389218909924207</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0.4054455361821754</v>
+      </c>
+      <c r="AL36" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="AM36" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q36" s="2" t="n">
+      <c r="AN36" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R36" s="2" t="n">
+      <c r="AO36" s="2" t="n">
         <v>46046.5</v>
       </c>
-      <c r="S36" s="2" t="n">
+      <c r="AP36" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T36" s="2" t="n">
+      <c r="AQ36" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="AR36" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="AS36" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="AT36" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="AU36" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>ORP-R3.0-Q_var-4603f19c2e35</t>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>ORP-R3.0-Q_var-5af2f4deaf7d</t>
         </is>
       </c>
     </row>
@@ -4125,66 +7005,147 @@
         <v>97</v>
       </c>
       <c r="K37" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L37" t="n">
         <v>10</v>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M37" t="n">
+        <v>25</v>
+      </c>
+      <c r="N37" t="n">
+        <v>6</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>exact_windows=97&lt;100</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W37" t="n">
+        <v>600</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.4824894968330908</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.6300516010775151</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.2626151670642995</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.6219930389356623</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.024592312992298</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.4898969230027386</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.4898969230027386</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.4185582822715436</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.7771821307760417</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.6357484296993684</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.5666600268334658</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0.8589942924981997</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.3979424529995605</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0.6357484296993684</v>
+      </c>
+      <c r="AL37" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="AM37" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="n">
+      <c r="AN37" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R37" s="2" t="n">
+      <c r="AO37" s="2" t="n">
         <v>46046.5</v>
       </c>
-      <c r="S37" s="2" t="n">
+      <c r="AP37" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T37" s="2" t="n">
+      <c r="AQ37" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="AR37" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="AS37" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="AT37" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="AU37" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>ORP-R1.0-Q_dist-f5a1c3e3fb3a</t>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>ORP-R1.0-Q_dist-bf80127306ec</t>
         </is>
       </c>
     </row>
@@ -4226,66 +7187,147 @@
         <v>97</v>
       </c>
       <c r="K38" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L38" t="n">
         <v>10</v>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M38" t="n">
+        <v>25</v>
+      </c>
+      <c r="N38" t="n">
+        <v>6</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>exact_windows=97&lt;100</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W38" t="n">
+        <v>600</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.5985820518043498</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.7502418485050047</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.2297938926284289</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.7238115348467804</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.178600773518999</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.4615209121692813</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.4615209121692813</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0.4662695368868882</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.9156739216637733</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0.6651000532375767</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0.6342481928705913</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1.014990487496999</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.4271186441579466</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0.6651000532375767</v>
+      </c>
+      <c r="AL38" t="inlineStr">
         <is>
           <t>construct_ablation_only</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="AM38" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="n">
+      <c r="AN38" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R38" s="2" t="n">
+      <c r="AO38" s="2" t="n">
         <v>46046.5</v>
       </c>
-      <c r="S38" s="2" t="n">
+      <c r="AP38" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T38" s="2" t="n">
+      <c r="AQ38" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="AR38" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="AS38" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="AT38" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="AU38" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>ORP-R1.0-Q_dist_w1_candidate-b949fdc6dbb4</t>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>ORP-R1.0-Q_dist_w1_candidate-9d3d1de571ae</t>
         </is>
       </c>
     </row>
@@ -4327,66 +7369,147 @@
         <v>97</v>
       </c>
       <c r="K39" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L39" t="n">
         <v>10</v>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M39" t="n">
+        <v>25</v>
+      </c>
+      <c r="N39" t="n">
+        <v>6</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>exact_windows=97&lt;100</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W39" t="n">
+        <v>600</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.2380952380952381</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.4663151041666665</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.7090711805555548</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0.3954397624434381</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.3954397624434381</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0.3680555555555556</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.5087152777777776</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.3528745644599297</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.39859375</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0.6222222222222222</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0.4149806701030932</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0.4149806701030932</v>
+      </c>
+      <c r="AL39" t="inlineStr">
         <is>
           <t>construct_ablation_only</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="AM39" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q39" s="2" t="n">
+      <c r="AN39" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R39" s="2" t="n">
+      <c r="AO39" s="2" t="n">
         <v>46046.5</v>
       </c>
-      <c r="S39" s="2" t="n">
+      <c r="AP39" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T39" s="2" t="n">
+      <c r="AQ39" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="AR39" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="AS39" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="AT39" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="AU39" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>ORP-R1.0-Q_dist_ks_candidate-b7073c096060</t>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>ORP-R1.0-Q_dist_ks_candidate-6c40b91c3f5b</t>
         </is>
       </c>
     </row>
@@ -4428,66 +7551,147 @@
         <v>97</v>
       </c>
       <c r="K40" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L40" t="n">
         <v>10</v>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M40" t="n">
+        <v>25</v>
+      </c>
+      <c r="N40" t="n">
+        <v>6</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>exact_windows=97&lt;100</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W40" t="n">
+        <v>600</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.700579276064471</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.568269768671017</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0.4157709275146524</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.385948672634195</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>3.321224101929518</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0.3255679603774952</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.4157709275146524</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.763359376719043</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>3.179695294998545</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0.4930243879827646</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>2.215533143853126</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>3.766630927986539</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.4636922642152261</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0.4930243879827646</v>
+      </c>
+      <c r="AL40" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="AM40" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q40" s="2" t="n">
+      <c r="AN40" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R40" s="2" t="n">
+      <c r="AO40" s="2" t="n">
         <v>46046.5</v>
       </c>
-      <c r="S40" s="2" t="n">
+      <c r="AP40" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T40" s="2" t="n">
+      <c r="AQ40" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="AR40" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="AS40" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="AT40" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="AU40" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>ORP-R1.0-Q_trend-658a313640a8</t>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>ORP-R1.0-Q_trend-7b4aae642334</t>
         </is>
       </c>
     </row>
@@ -4529,66 +7733,147 @@
         <v>97</v>
       </c>
       <c r="K41" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L41" t="n">
         <v>10</v>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M41" t="n">
+        <v>25</v>
+      </c>
+      <c r="N41" t="n">
+        <v>6</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>exact_windows=97&lt;100</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W41" t="n">
+        <v>600</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.4707801262460918</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0.6273916919254203</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0.2689011060485301</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.6465287658966179</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.7485235919388744</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0.147081439635954</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.2689011060485301</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0.4283759421472749</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0.6640613801645047</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.3791346826121847</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0.5920801701476635</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0.7438765107313288</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0.2213958018162836</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0.3791346826121847</v>
+      </c>
+      <c r="AL41" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="AM41" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q41" s="2" t="n">
+      <c r="AN41" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R41" s="2" t="n">
+      <c r="AO41" s="2" t="n">
         <v>46046.5</v>
       </c>
-      <c r="S41" s="2" t="n">
+      <c r="AP41" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T41" s="2" t="n">
+      <c r="AQ41" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="AR41" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="AS41" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="AT41" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="AU41" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>ORP-R1.0-Q_var-9bcb67fcbaf1</t>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>ORP-R1.0-Q_var-5737a660597d</t>
         </is>
       </c>
     </row>
@@ -4630,66 +7915,147 @@
         <v>23</v>
       </c>
       <c r="K42" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L42" t="n">
-        <v>3</v>
-      </c>
-      <c r="M42" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M42" t="n">
+        <v>25</v>
+      </c>
+      <c r="N42" t="n">
+        <v>6</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>exact_windows=23&lt;100; exact_independent_blocks=4&lt;6</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W42" t="n">
+        <v>600</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.486240710540256</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0.6286357584272232</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0.2534193957279368</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.6287273109505491</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.9933776509203416</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0.4437193284605214</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.4437193284605214</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0.4198784194687565</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0.5776308481366561</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.2949261052860222</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0.424162518996619</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0.5776308481366561</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0.2699204355923221</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0.2949261052860222</v>
+      </c>
+      <c r="AL42" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="AM42" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q42" s="2" t="n">
+      <c r="AN42" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R42" s="2" t="n">
+      <c r="AO42" s="2" t="n">
         <v>46046.5</v>
       </c>
-      <c r="S42" s="2" t="n">
+      <c r="AP42" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T42" s="2" t="n">
+      <c r="AQ42" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="AR42" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="AS42" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="AT42" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="AU42" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>ORP-R0.0-Q_dist-7a1ec31e2292</t>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>ORP-R0.0-Q_dist-4e2069bbaa4c</t>
         </is>
       </c>
     </row>
@@ -4731,66 +8097,147 @@
         <v>23</v>
       </c>
       <c r="K43" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L43" t="n">
-        <v>3</v>
-      </c>
-      <c r="M43" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M43" t="n">
+        <v>25</v>
+      </c>
+      <c r="N43" t="n">
+        <v>6</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>exact_windows=23&lt;100; exact_independent_blocks=4&lt;6</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W43" t="n">
+        <v>600</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0.6013348537043763</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0.7506012545763362</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0.2261674355446042</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.7235153430656437</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.150188686939213</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0.4329888531174608</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0.4329888531174608</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0.3960999416914252</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0.6609296132923554</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0.4388106218540016</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0.4139503563908523</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0.6664217839314638</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0.3876313959741974</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0.4388106218540016</v>
+      </c>
+      <c r="AL43" t="inlineStr">
         <is>
           <t>construct_ablation_only</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="AM43" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q43" s="2" t="n">
+      <c r="AN43" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R43" s="2" t="n">
+      <c r="AO43" s="2" t="n">
         <v>46046.5</v>
       </c>
-      <c r="S43" s="2" t="n">
+      <c r="AP43" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T43" s="2" t="n">
+      <c r="AQ43" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="AR43" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="AS43" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="AT43" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="AU43" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>ORP-R0.0-Q_dist_w1_candidate-0c6b33ac2473</t>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>ORP-R0.0-Q_dist_w1_candidate-7d77f865d552</t>
         </is>
       </c>
     </row>
@@ -4832,66 +8279,147 @@
         <v>23</v>
       </c>
       <c r="K44" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L44" t="n">
-        <v>3</v>
-      </c>
-      <c r="M44" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M44" t="n">
+        <v>25</v>
+      </c>
+      <c r="N44" t="n">
+        <v>6</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>exact_windows=23&lt;100; exact_independent_blocks=4&lt;6</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W44" t="n">
+        <v>600</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.3763715277777777</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.2349603174603178</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.4722135416666667</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.7083723958333332</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0.3846931561085971</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.3846931561085971</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0.3541666666666666</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0.2169811320754718</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0.3819444444444445</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0.1551590380139642</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0.2169811320754718</v>
+      </c>
+      <c r="AL44" t="inlineStr">
         <is>
           <t>construct_ablation_only</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="AM44" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q44" s="2" t="n">
+      <c r="AN44" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R44" s="2" t="n">
+      <c r="AO44" s="2" t="n">
         <v>46046.5</v>
       </c>
-      <c r="S44" s="2" t="n">
+      <c r="AP44" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T44" s="2" t="n">
+      <c r="AQ44" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="AR44" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="AS44" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="AT44" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="AU44" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>ORP-R0.0-Q_dist_ks_candidate-607de4e743f0</t>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>ORP-R0.0-Q_dist_ks_candidate-99ebcefc19ac</t>
         </is>
       </c>
     </row>
@@ -4933,66 +8461,147 @@
         <v>23</v>
       </c>
       <c r="K45" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L45" t="n">
-        <v>3</v>
-      </c>
-      <c r="M45" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M45" t="n">
+        <v>25</v>
+      </c>
+      <c r="N45" t="n">
+        <v>6</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>exact_windows=23&lt;100; exact_independent_blocks=4&lt;6</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W45" t="n">
+        <v>600</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.680352261840316</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>2.577712705574215</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0.4299878668549422</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.367183145519745</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>3.310697896914029</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0.3284360559209361</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.4299878668549422</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.621003689615923</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>2.501172173127561</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0.4067025071622126</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1.937857369773285</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>2.501172173127561</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0.2299564819570667</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0.4067025071622126</v>
+      </c>
+      <c r="AL45" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="AM45" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q45" s="2" t="n">
+      <c r="AN45" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R45" s="2" t="n">
+      <c r="AO45" s="2" t="n">
         <v>46046.5</v>
       </c>
-      <c r="S45" s="2" t="n">
+      <c r="AP45" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T45" s="2" t="n">
+      <c r="AQ45" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="AR45" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="AS45" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="AT45" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="AU45" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>ORP-R0.0-Q_trend-5519749caadb</t>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>ORP-R0.0-Q_trend-f97b869d440a</t>
         </is>
       </c>
     </row>
@@ -5034,66 +8643,147 @@
         <v>23</v>
       </c>
       <c r="K46" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L46" t="n">
-        <v>3</v>
-      </c>
-      <c r="M46" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M46" t="n">
+        <v>25</v>
+      </c>
+      <c r="N46" t="n">
+        <v>6</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>exact_windows=23&lt;100; exact_independent_blocks=4&lt;6</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>wide_interval</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W46" t="n">
+        <v>600</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0.4707646849113584</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0.6313903108720883</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0.2757932231455803</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0.6443164863610478</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.7499358613332161</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0.1523082133393723</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.2757932231455803</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0.2615999449061395</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0.7515157032881844</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.057768892072747</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0.2758617018393439</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0.7515157032881844</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0.7965807496982007</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1.057768892072747</v>
+      </c>
+      <c r="AL46" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="AM46" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q46" s="2" t="n">
+      <c r="AN46" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R46" s="2" t="n">
+      <c r="AO46" s="2" t="n">
         <v>46046.5</v>
       </c>
-      <c r="S46" s="2" t="n">
+      <c r="AP46" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T46" s="2" t="n">
+      <c r="AQ46" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="AR46" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="AS46" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="AT46" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="AU46" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>ORP-R0.0-Q_var-a111b81afb9f</t>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>ORP-R0.0-Q_var-94b746bcb4a1</t>
         </is>
       </c>
     </row>
@@ -5133,66 +8823,133 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M47" t="n">
+        <v>25</v>
+      </c>
+      <c r="N47" t="n">
+        <v>6</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>exact_windows=0&lt;100; exact_independent_blocks=0&lt;6</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>insufficient_independent_support</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W47" t="n">
+        <v>600</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.4854898457259077</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0.6286413344588248</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0.2547656278120519</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0.6253853792303697</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.001047920446569</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0.4571193613312776</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.4571193613312776</v>
+      </c>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="AM47" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q47" s="2" t="n">
+      <c r="AN47" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R47" s="2" t="n">
+      <c r="AO47" s="2" t="n">
         <v>46046.5</v>
       </c>
-      <c r="S47" s="2" t="n">
+      <c r="AP47" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T47" s="2" t="n">
+      <c r="AQ47" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="AR47" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="AS47" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="AT47" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="AU47" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>ORP-Rnan-Q_dist-5b8d87b6ea99</t>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>ORP-Rnan-Q_dist-23f31f5260e4</t>
         </is>
       </c>
     </row>
@@ -5232,66 +8989,133 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="M48" t="n">
+        <v>25</v>
+      </c>
+      <c r="N48" t="n">
+        <v>6</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>exact_windows=0&lt;100; exact_independent_blocks=0&lt;6</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>insufficient_independent_support</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W48" t="n">
+        <v>600</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0.5985404667090396</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0.7502418485050047</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0.2298569020820516</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0.7350082199232624</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.170877369094948</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0.4423207723636348</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.4423207723636348</v>
+      </c>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr">
         <is>
           <t>construct_ablation_only</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="AM48" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q48" s="2" t="n">
+      <c r="AN48" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R48" s="2" t="n">
+      <c r="AO48" s="2" t="n">
         <v>46046.5</v>
       </c>
-      <c r="S48" s="2" t="n">
+      <c r="AP48" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T48" s="2" t="n">
+      <c r="AQ48" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="AR48" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="AS48" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="AT48" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="AU48" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>ORP-Rnan-Q_dist_w1_candidate-8df0e566bc49</t>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>ORP-Rnan-Q_dist_w1_candidate-911bfafced71</t>
         </is>
       </c>
     </row>
@@ -5331,66 +9155,133 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M49" t="n">
+        <v>25</v>
+      </c>
+      <c r="N49" t="n">
+        <v>6</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>exact_windows=0&lt;100; exact_independent_blocks=0&lt;6</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>insufficient_independent_support</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W49" t="n">
+        <v>600</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0.3819444444444445</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0.4749913194444443</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0.7087630208333329</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0.3808045814479633</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.3808045814479633</v>
+      </c>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr">
         <is>
           <t>construct_ablation_only</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="AM49" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q49" s="2" t="n">
+      <c r="AN49" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R49" s="2" t="n">
+      <c r="AO49" s="2" t="n">
         <v>46046.5</v>
       </c>
-      <c r="S49" s="2" t="n">
+      <c r="AP49" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T49" s="2" t="n">
+      <c r="AQ49" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="AR49" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="AS49" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="AT49" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="AU49" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>ORP-Rnan-Q_dist_ks_candidate-fb0ed96f57f8</t>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>ORP-Rnan-Q_dist_ks_candidate-c317a4b422f0</t>
         </is>
       </c>
     </row>
@@ -5430,66 +9321,133 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="M50" t="n">
+        <v>25</v>
+      </c>
+      <c r="N50" t="n">
+        <v>6</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>exact_windows=0&lt;100; exact_independent_blocks=0&lt;6</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>insufficient_independent_support</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W50" t="n">
+        <v>600</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1.674178394213148</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>2.571214287838041</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0.4298323523010822</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>2.393875569477343</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>3.218792627913223</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0.2871523786291724</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.4298323523010822</v>
+      </c>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="AM50" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q50" s="2" t="n">
+      <c r="AN50" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R50" s="2" t="n">
+      <c r="AO50" s="2" t="n">
         <v>46046.5</v>
       </c>
-      <c r="S50" s="2" t="n">
+      <c r="AP50" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T50" s="2" t="n">
+      <c r="AQ50" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="AR50" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="AS50" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="AT50" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="AU50" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>ORP-Rnan-Q_trend-212058677f5a</t>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>ORP-Rnan-Q_trend-8f660b8e3065</t>
         </is>
       </c>
     </row>
@@ -5529,66 +9487,133 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="M51" t="n">
+        <v>25</v>
+      </c>
+      <c r="N51" t="n">
+        <v>6</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>exact_windows=0&lt;100; exact_independent_blocks=0&lt;6</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
         <is>
           <t>variable_public_fallback</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>fallback_limited_regime_support</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>insufficient_independent_support</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
+        </is>
+      </c>
+      <c r="W51" t="n">
+        <v>600</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0.4742427828664413</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0.6353796346111951</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0.2766709947084163</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0.6443164863610478</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0.7494689444801284</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0.1516348968035513</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.2766709947084163</v>
+      </c>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="AM51" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="Q51" s="2" t="n">
+      <c r="AN51" s="2" t="n">
         <v>45871.95833333334</v>
       </c>
-      <c r="R51" s="2" t="n">
+      <c r="AO51" s="2" t="n">
         <v>46046.5</v>
       </c>
-      <c r="S51" s="2" t="n">
+      <c r="AP51" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="T51" s="2" t="n">
+      <c r="AQ51" s="2" t="n">
         <v>46046.99998842592</v>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="AR51" t="inlineStr">
         <is>
           <t>synchronous_timestamp_primary</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="AS51" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="AT51" t="inlineStr">
         <is>
           <t>development_only_high_quality_common_support_external_D5_gate</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="AU51" t="inlineStr">
         <is>
           <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>ORP-Rnan-Q_var-c9c1a5d10dfb</t>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>ORP-Rnan-Q_var-bde17a1c8548</t>
         </is>
       </c>
     </row>
@@ -5725,7 +9750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5774,21 +9799,36 @@
           <t>distribution_component_version</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>calibration_support_rule</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>min_exact_independent_blocks</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>percentile_precision_role</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d4-v1.5-common-support-frozen-d4-20260813</t>
+          <t>d4-v1.5.1-statistical-dependence-audit-20260813</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>D4V15_20260813_033216</t>
+          <t>D4V151_20260813_083347</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -5819,6 +9859,19 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>full_w1_0.60_ks_0.40_development_frozen</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>minimum_windows_and_independent_7d_blocks</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>evidence_grade_only_pending_preregistered_precision_target</t>
         </is>
       </c>
     </row>
